--- a/exports/ADANIGREEN_full_report.xlsx
+++ b/exports/ADANIGREEN_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q71"/>
+  <dimension ref="A1:U71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>5.66</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44606.55208333334</v>
+        <v>44607.38541666666</v>
       </c>
       <c r="H2" t="n">
-        <v>1852.5</v>
+        <v>1833.6</v>
       </c>
       <c r="I2" t="n">
         <v>1846.21285531087</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>35.16666666666666</v>
+        <v>36</v>
       </c>
       <c r="K2" t="n">
-        <v>29.99</v>
+        <v>28.66</v>
       </c>
       <c r="L2" t="n">
         <v>1.41</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -591,28 +626,28 @@
         <v>9.359999999999999</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44608.55208333334</v>
+        <v>44609.38541666666</v>
       </c>
       <c r="H3" t="n">
-        <v>1914</v>
+        <v>2054</v>
       </c>
       <c r="I3" t="n">
         <v>2005.163658952246</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>1.166666666666667</v>
+        <v>2</v>
       </c>
       <c r="K3" t="n">
-        <v>-4.38</v>
+        <v>-12.02</v>
       </c>
       <c r="L3" t="n">
-        <v>7.38</v>
+        <v>14.25</v>
       </c>
       <c r="M3" t="n">
-        <v>1.48</v>
+        <v>1.88</v>
       </c>
       <c r="N3" t="n">
-        <v>1.86</v>
+        <v>7</v>
       </c>
       <c r="O3" t="n">
         <v>1.86</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S3" t="b">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -648,22 +695,22 @@
         <v>12.7</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44616.38541666666</v>
+        <v>44616.55208333334</v>
       </c>
       <c r="H4" t="n">
-        <v>1911</v>
+        <v>1815</v>
       </c>
       <c r="I4" t="n">
         <v>1873.118335072759</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>7</v>
+        <v>7.166666666666667</v>
       </c>
       <c r="K4" t="n">
-        <v>-6.96</v>
+        <v>-11.64</v>
       </c>
       <c r="L4" t="n">
-        <v>9.93</v>
+        <v>12.36</v>
       </c>
       <c r="M4" t="n">
         <v>5.06</v>
@@ -678,7 +725,19 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -705,22 +764,22 @@
         <v>15.68</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44649.55208333334</v>
+        <v>44650.38541666666</v>
       </c>
       <c r="H5" t="n">
-        <v>1926</v>
+        <v>2009.9</v>
       </c>
       <c r="I5" t="n">
         <v>1955.566358165647</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>33</v>
+        <v>33.83333333333334</v>
       </c>
       <c r="K5" t="n">
-        <v>-6.12</v>
+        <v>-10.74</v>
       </c>
       <c r="L5" t="n">
-        <v>10.01</v>
+        <v>12.39</v>
       </c>
       <c r="M5" t="n">
         <v>3.31</v>
@@ -735,7 +794,19 @@
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S5" t="b">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -762,25 +833,25 @@
         <v>8.51</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44650.38541666666</v>
+        <v>44650.55208333334</v>
       </c>
       <c r="H6" t="n">
-        <v>2009.9</v>
+        <v>1829</v>
       </c>
       <c r="I6" t="n">
         <v>1838.846837078114</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>-9</v>
       </c>
       <c r="L6" t="n">
-        <v>3.68</v>
+        <v>11.4</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="N6" t="n">
         <v>5.04</v>
@@ -792,7 +863,19 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -819,22 +902,22 @@
         <v>15.6</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44655.38541666666</v>
+        <v>44655.55208333334</v>
       </c>
       <c r="H7" t="n">
-        <v>1997.05</v>
+        <v>2136.65</v>
       </c>
       <c r="I7" t="n">
         <v>2114.287846629698</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>4.833333333333333</v>
+        <v>5</v>
       </c>
       <c r="K7" t="n">
-        <v>-9.19</v>
+        <v>-16.82</v>
       </c>
       <c r="L7" t="n">
-        <v>10.99</v>
+        <v>16.98</v>
       </c>
       <c r="M7" t="n">
         <v>3.34</v>
@@ -849,7 +932,19 @@
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>13.76</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44690.55208333334</v>
+        <v>44691.38541666666</v>
       </c>
       <c r="H8" t="n">
-        <v>2690</v>
+        <v>2580</v>
       </c>
       <c r="I8" t="n">
         <v>2632.861189937932</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>35</v>
+        <v>35.83333333333334</v>
       </c>
       <c r="K8" t="n">
-        <v>25.9</v>
+        <v>20.75</v>
       </c>
       <c r="L8" t="n">
         <v>6.53</v>
@@ -897,7 +992,7 @@
         <v>1.95</v>
       </c>
       <c r="N8" t="n">
-        <v>6.05</v>
+        <v>7.25</v>
       </c>
       <c r="O8" t="n">
         <v>9.18</v>
@@ -906,7 +1001,19 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>16.72</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44736.55208333334</v>
+        <v>44739.38541666666</v>
       </c>
       <c r="H9" t="n">
-        <v>1846</v>
+        <v>1903</v>
       </c>
       <c r="I9" t="n">
         <v>1875.772066101633</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>45.16666666666666</v>
+        <v>48</v>
       </c>
       <c r="K9" t="n">
-        <v>28.45</v>
+        <v>26.24</v>
       </c>
       <c r="L9" t="n">
         <v>6.15</v>
@@ -963,7 +1070,19 @@
         <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>68</v>
+        <v>69</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>10.26</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44755.55208333334</v>
+        <v>44756.38541666666</v>
       </c>
       <c r="H10" t="n">
-        <v>2124.25</v>
+        <v>1969.05</v>
       </c>
       <c r="I10" t="n">
         <v>2075.165309704487</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>16.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K10" t="n">
-        <v>11.63</v>
+        <v>3.47</v>
       </c>
       <c r="L10" t="n">
         <v>2.24</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -1047,22 +1178,22 @@
         <v>21.14</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44774.38541666666</v>
+        <v>44774.55208333334</v>
       </c>
       <c r="H11" t="n">
-        <v>2236.35</v>
+        <v>2274</v>
       </c>
       <c r="I11" t="n">
         <v>2246.889617133148</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>18</v>
+        <v>18.16666666666667</v>
       </c>
       <c r="K11" t="n">
-        <v>-13.58</v>
+        <v>-15.49</v>
       </c>
       <c r="L11" t="n">
-        <v>14.27</v>
+        <v>16.34</v>
       </c>
       <c r="M11" t="n">
         <v>1.68</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,22 +1247,22 @@
         <v>7.98</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44778.38541666666</v>
+        <v>44778.55208333334</v>
       </c>
       <c r="H12" t="n">
-        <v>2173</v>
+        <v>2099</v>
       </c>
       <c r="I12" t="n">
         <v>2136.060557440725</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>3.833333333333333</v>
+        <v>4</v>
       </c>
       <c r="K12" t="n">
-        <v>-4.44</v>
+        <v>-7.7</v>
       </c>
       <c r="L12" t="n">
-        <v>4.97</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="M12" t="n">
         <v>0.05</v>
@@ -1134,7 +1277,19 @@
         <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S12" t="b">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1161,28 +1316,28 @@
         <v>10.81</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44791.55208333334</v>
+        <v>44792.38541666666</v>
       </c>
       <c r="H13" t="n">
-        <v>2282</v>
+        <v>2441.65</v>
       </c>
       <c r="I13" t="n">
         <v>2323.789844066675</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>13</v>
+        <v>13.83333333333333</v>
       </c>
       <c r="K13" t="n">
-        <v>-8.720000000000001</v>
+        <v>-16.32</v>
       </c>
       <c r="L13" t="n">
-        <v>11.64</v>
+        <v>18.28</v>
       </c>
       <c r="M13" t="n">
-        <v>0.74</v>
+        <v>1.45</v>
       </c>
       <c r="N13" t="n">
-        <v>3.57</v>
+        <v>6.16</v>
       </c>
       <c r="O13" t="n">
         <v>-4.07</v>
@@ -1191,7 +1346,19 @@
         <v>1</v>
       </c>
       <c r="Q13" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S13" t="b">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>9.859999999999999</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44818.38541666666</v>
+        <v>44818.55208333334</v>
       </c>
       <c r="H14" t="n">
-        <v>2300</v>
+        <v>2295</v>
       </c>
       <c r="I14" t="n">
         <v>2299.729703056154</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>26</v>
+        <v>26.16666666666667</v>
       </c>
       <c r="K14" t="n">
-        <v>-5.8</v>
+        <v>-6.01</v>
       </c>
       <c r="L14" t="n">
         <v>9.9</v>
@@ -1248,7 +1415,19 @@
         <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>7.71</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>44833.55208333334</v>
+        <v>44834.38541666666</v>
       </c>
       <c r="H15" t="n">
-        <v>1989</v>
+        <v>2260.25</v>
       </c>
       <c r="I15" t="n">
         <v>2253.947780497941</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>15</v>
+        <v>15.83333333333333</v>
       </c>
       <c r="K15" t="n">
-        <v>13.33</v>
+        <v>1.51</v>
       </c>
       <c r="L15" t="n">
         <v>6.14</v>
@@ -1296,7 +1475,7 @@
         <v>2.03</v>
       </c>
       <c r="N15" t="n">
-        <v>2.21</v>
+        <v>13.29</v>
       </c>
       <c r="O15" t="n">
         <v>-1.67</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>16.84</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>44882.55208333334</v>
+        <v>44883.38541666666</v>
       </c>
       <c r="H16" t="n">
-        <v>2109</v>
+        <v>2060.85</v>
       </c>
       <c r="I16" t="n">
         <v>2084.745630219701</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>48.16666666666666</v>
+        <v>49</v>
       </c>
       <c r="K16" t="n">
-        <v>-6.69</v>
+        <v>-8.82</v>
       </c>
       <c r="L16" t="n">
         <v>11.62</v>
@@ -1362,7 +1553,19 @@
         <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>63</v>
+        <v>64</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1389,22 +1592,22 @@
         <v>7.48</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>44895.38541666666</v>
+        <v>44895.55208333334</v>
       </c>
       <c r="H17" t="n">
-        <v>2021.1</v>
+        <v>2123.05</v>
       </c>
       <c r="I17" t="n">
         <v>2111.17595560919</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>12</v>
+        <v>12.16666666666667</v>
       </c>
       <c r="K17" t="n">
-        <v>1.93</v>
+        <v>-3.02</v>
       </c>
       <c r="L17" t="n">
-        <v>2.97</v>
+        <v>4</v>
       </c>
       <c r="M17" t="n">
         <v>0.8100000000000001</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,22 +1661,22 @@
         <v>8.57</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>44916.38541666666</v>
+        <v>44916.55208333334</v>
       </c>
       <c r="H18" t="n">
-        <v>2028.2</v>
+        <v>1977</v>
       </c>
       <c r="I18" t="n">
         <v>1994.300419307244</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>20.83333333333333</v>
+        <v>21</v>
       </c>
       <c r="K18" t="n">
-        <v>-4.47</v>
+        <v>-6.88</v>
       </c>
       <c r="L18" t="n">
-        <v>5.8</v>
+        <v>9.44</v>
       </c>
       <c r="M18" t="n">
         <v>1.12</v>
@@ -1476,7 +1691,19 @@
         <v>1</v>
       </c>
       <c r="Q18" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S18" t="b">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1503,28 +1730,28 @@
         <v>6.75</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>44939.55208333334</v>
+        <v>44942.38541666666</v>
       </c>
       <c r="H19" t="n">
-        <v>1909.95</v>
+        <v>2036.2</v>
       </c>
       <c r="I19" t="n">
         <v>1972.835867941542</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>23</v>
+        <v>25.83333333333333</v>
       </c>
       <c r="K19" t="n">
-        <v>3.39</v>
+        <v>-2.99</v>
       </c>
       <c r="L19" t="n">
-        <v>2.9</v>
+        <v>3.16</v>
       </c>
       <c r="M19" t="n">
         <v>1.15</v>
       </c>
       <c r="N19" t="n">
-        <v>3.94</v>
+        <v>10.11</v>
       </c>
       <c r="O19" t="n">
         <v>-3.74</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>9.35</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>44944.55208333334</v>
+        <v>44945.38541666666</v>
       </c>
       <c r="H20" t="n">
-        <v>2085.85</v>
+        <v>1994.3</v>
       </c>
       <c r="I20" t="n">
         <v>2014.036586655662</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>2.166666666666667</v>
+        <v>3</v>
       </c>
       <c r="K20" t="n">
-        <v>2.44</v>
+        <v>-2.06</v>
       </c>
       <c r="L20" t="n">
         <v>5.46</v>
@@ -1581,7 +1820,7 @@
         <v>0.03</v>
       </c>
       <c r="N20" t="n">
-        <v>3.66</v>
+        <v>6.32</v>
       </c>
       <c r="O20" t="n">
         <v>10.11</v>
@@ -1590,7 +1829,19 @@
         <v>1</v>
       </c>
       <c r="Q20" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S20" t="b">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>10.53</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>44986.55208333334</v>
+        <v>44987.38541666666</v>
       </c>
       <c r="H21" t="n">
-        <v>509.55</v>
+        <v>535</v>
       </c>
       <c r="I21" t="n">
         <v>517.7118584353341</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>41.16666666666666</v>
+        <v>42</v>
       </c>
       <c r="K21" t="n">
-        <v>74.45</v>
+        <v>73.17</v>
       </c>
       <c r="L21" t="n">
         <v>4.7</v>
@@ -1647,7 +1898,19 @@
         <v>1</v>
       </c>
       <c r="Q21" t="n">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>3</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>10.67</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45014.38541666666</v>
+        <v>45014.55208333334</v>
       </c>
       <c r="H22" t="n">
-        <v>938</v>
+        <v>897.9</v>
       </c>
       <c r="I22" t="n">
         <v>929.1117752126378</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>27</v>
+        <v>27.16666666666667</v>
       </c>
       <c r="K22" t="n">
-        <v>75.33</v>
+        <v>67.83</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -1704,7 +1967,19 @@
         <v>1</v>
       </c>
       <c r="Q22" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S22" t="b">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>16.64</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45026.55208333334</v>
+        <v>45027.38541666666</v>
       </c>
       <c r="H23" t="n">
-        <v>899.15</v>
+        <v>944.1</v>
       </c>
       <c r="I23" t="n">
         <v>935.4851161212116</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>12</v>
+        <v>12.83333333333333</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.14</v>
+        <v>-5.15</v>
       </c>
       <c r="L23" t="n">
         <v>6.03</v>
@@ -1761,7 +2036,19 @@
         <v>1</v>
       </c>
       <c r="Q23" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S23" t="b">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>11.67</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45057.55208333334</v>
+        <v>45058.38541666666</v>
       </c>
       <c r="H24" t="n">
-        <v>915</v>
+        <v>897.8</v>
       </c>
       <c r="I24" t="n">
         <v>898.6147860382437</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>30.16666666666667</v>
+        <v>31</v>
       </c>
       <c r="K24" t="n">
-        <v>-3.08</v>
+        <v>-4.9</v>
       </c>
       <c r="L24" t="n">
         <v>8.1</v>
@@ -1818,7 +2105,19 @@
         <v>1</v>
       </c>
       <c r="Q24" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>7.32</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45065.38541666666</v>
+        <v>45065.55208333334</v>
       </c>
       <c r="H25" t="n">
-        <v>839.95</v>
+        <v>903.55</v>
       </c>
       <c r="I25" t="n">
         <v>894.9525695605695</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>7</v>
+        <v>7.166666666666667</v>
       </c>
       <c r="K25" t="n">
-        <v>6.44</v>
+        <v>-0.64</v>
       </c>
       <c r="L25" t="n">
         <v>2.47</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S25" t="b">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>12</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45140.55208333334</v>
+        <v>45141.38541666666</v>
       </c>
       <c r="H26" t="n">
-        <v>1050</v>
+        <v>1039.55</v>
       </c>
       <c r="I26" t="n">
         <v>1045.959789168084</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>75</v>
+        <v>75.83333333333333</v>
       </c>
       <c r="K26" t="n">
-        <v>16.21</v>
+        <v>15.05</v>
       </c>
       <c r="L26" t="n">
         <v>7.19</v>
@@ -1932,7 +2243,19 @@
         <v>1</v>
       </c>
       <c r="Q26" t="n">
-        <v>105</v>
+        <v>106</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>4</v>
+      </c>
+      <c r="U26" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="27">
@@ -1959,19 +2282,19 @@
         <v>10.41</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45156.55208333334</v>
+        <v>45159.38541666666</v>
       </c>
       <c r="H27" t="n">
-        <v>999</v>
+        <v>1022.5</v>
       </c>
       <c r="I27" t="n">
         <v>1003.034044035462</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>18</v>
       </c>
       <c r="K27" t="n">
-        <v>3.9</v>
+        <v>1.64</v>
       </c>
       <c r="L27" t="n">
         <v>2.64</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S27" t="b">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>9.23</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45169.38541666666</v>
+        <v>45169.55208333334</v>
       </c>
       <c r="H28" t="n">
-        <v>938.75</v>
+        <v>934</v>
       </c>
       <c r="I28" t="n">
         <v>938.5607248375002</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>10</v>
+        <v>10.16666666666667</v>
       </c>
       <c r="K28" t="n">
-        <v>-8.19</v>
+        <v>-8.66</v>
       </c>
       <c r="L28" t="n">
         <v>9.960000000000001</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S28" t="b">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -2073,22 +2420,22 @@
         <v>7.29</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45175.38541666666</v>
+        <v>45175.55208333334</v>
       </c>
       <c r="H29" t="n">
-        <v>974.05</v>
+        <v>1006.5</v>
       </c>
       <c r="I29" t="n">
         <v>999.6105012457224</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>5.833333333333333</v>
+        <v>6</v>
       </c>
       <c r="K29" t="n">
-        <v>-4.29</v>
+        <v>-7.76</v>
       </c>
       <c r="L29" t="n">
-        <v>4.92</v>
+        <v>8.67</v>
       </c>
       <c r="M29" t="n">
         <v>0.52</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S29" t="b">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -2130,22 +2489,22 @@
         <v>8.18</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45204.38541666666</v>
+        <v>45204.55208333334</v>
       </c>
       <c r="H30" t="n">
-        <v>970.85</v>
+        <v>958.05</v>
       </c>
       <c r="I30" t="n">
         <v>964.4716751803392</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>28.83333333333333</v>
+        <v>29</v>
       </c>
       <c r="K30" t="n">
-        <v>-3.54</v>
+        <v>-4.81</v>
       </c>
       <c r="L30" t="n">
-        <v>4.1</v>
+        <v>5.12</v>
       </c>
       <c r="M30" t="n">
         <v>0.49</v>
@@ -2160,7 +2519,19 @@
         <v>1</v>
       </c>
       <c r="Q30" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>5.87</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45229.38541666666</v>
+        <v>45229.55208333334</v>
       </c>
       <c r="H31" t="n">
-        <v>890.45</v>
+        <v>913.8</v>
       </c>
       <c r="I31" t="n">
         <v>913.1935418574852</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>24.83333333333333</v>
+        <v>25</v>
       </c>
       <c r="K31" t="n">
-        <v>7.06</v>
+        <v>4.62</v>
       </c>
       <c r="L31" t="n">
         <v>1.34</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>9.359999999999999</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45308.55208333334</v>
+        <v>45309.38541666666</v>
       </c>
       <c r="H32" t="n">
-        <v>1613.9</v>
+        <v>1586.35</v>
       </c>
       <c r="I32" t="n">
         <v>1609.137283428433</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>79</v>
+        <v>79.83333333333333</v>
       </c>
       <c r="K32" t="n">
-        <v>76.61</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="L32" t="n">
         <v>4.14</v>
@@ -2274,7 +2657,19 @@
         <v>1</v>
       </c>
       <c r="Q32" t="n">
-        <v>110</v>
+        <v>111</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>3</v>
+      </c>
+      <c r="U32" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>7.8</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45316.55208333334</v>
+        <v>45320.38541666666</v>
       </c>
       <c r="H33" t="n">
-        <v>1661.05</v>
+        <v>1712.1</v>
       </c>
       <c r="I33" t="n">
         <v>1683.838969093114</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>11</v>
       </c>
       <c r="K33" t="n">
-        <v>-4.71</v>
+        <v>-7.93</v>
       </c>
       <c r="L33" t="n">
         <v>10</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2358,28 +2765,28 @@
         <v>9.050000000000001</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45363.55208333334</v>
+        <v>45364.38541666666</v>
       </c>
       <c r="H34" t="n">
-        <v>1893.75</v>
+        <v>1777.1</v>
       </c>
       <c r="I34" t="n">
         <v>1841.210692661985</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>43.16666666666666</v>
+        <v>44</v>
       </c>
       <c r="K34" t="n">
-        <v>10.61</v>
+        <v>3.8</v>
       </c>
       <c r="L34" t="n">
-        <v>3.53</v>
+        <v>3.63</v>
       </c>
       <c r="M34" t="n">
         <v>0.66</v>
       </c>
       <c r="N34" t="n">
-        <v>2.53</v>
+        <v>8.17</v>
       </c>
       <c r="O34" t="n">
         <v>3.19</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>61</v>
+        <v>62</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2415,19 +2834,19 @@
         <v>12</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45427.38541666666</v>
+        <v>45427.55208333334</v>
       </c>
       <c r="H35" t="n">
-        <v>1826.55</v>
+        <v>1835</v>
       </c>
       <c r="I35" t="n">
         <v>1834.514822351049</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>63</v>
+        <v>63.16666666666666</v>
       </c>
       <c r="K35" t="n">
-        <v>-2.78</v>
+        <v>-3.26</v>
       </c>
       <c r="L35" t="n">
         <v>11.13</v>
@@ -2445,7 +2864,19 @@
         <v>1</v>
       </c>
       <c r="Q35" t="n">
-        <v>81</v>
+        <v>82</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>3</v>
+      </c>
+      <c r="U35" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="36">
@@ -2472,28 +2903,28 @@
         <v>7.98</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45446.55208333334</v>
+        <v>45447.38541666666</v>
       </c>
       <c r="H36" t="n">
-        <v>2042.85</v>
+        <v>1698.8</v>
       </c>
       <c r="I36" t="n">
         <v>1846.690843370717</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>19</v>
+        <v>19.83333333333333</v>
       </c>
       <c r="K36" t="n">
-        <v>11.33</v>
+        <v>-7.42</v>
       </c>
       <c r="L36" t="n">
-        <v>1.53</v>
+        <v>11.15</v>
       </c>
       <c r="M36" t="n">
         <v>0.73</v>
       </c>
       <c r="N36" t="n">
-        <v>2.19</v>
+        <v>19.62</v>
       </c>
       <c r="O36" t="n">
         <v>2.74</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2529,19 +2972,19 @@
         <v>26.09</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45498.38541666666</v>
+        <v>45498.55208333334</v>
       </c>
       <c r="H37" t="n">
-        <v>1737.3</v>
+        <v>1848</v>
       </c>
       <c r="I37" t="n">
         <v>1806.281665475373</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>51</v>
+        <v>51.16666666666666</v>
       </c>
       <c r="K37" t="n">
-        <v>-2.27</v>
+        <v>-8.779999999999999</v>
       </c>
       <c r="L37" t="n">
         <v>19.49</v>
@@ -2559,7 +3002,19 @@
         <v>1</v>
       </c>
       <c r="Q37" t="n">
-        <v>71</v>
+        <v>72</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>10.6</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45547.38541666666</v>
+        <v>45547.55208333334</v>
       </c>
       <c r="H38" t="n">
-        <v>1821.95</v>
+        <v>1806</v>
       </c>
       <c r="I38" t="n">
         <v>1808.8438969818</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>48.83333333333334</v>
+        <v>49</v>
       </c>
       <c r="K38" t="n">
-        <v>-1.41</v>
+        <v>-2.27</v>
       </c>
       <c r="L38" t="n">
         <v>9.77</v>
@@ -2616,7 +3071,19 @@
         <v>1</v>
       </c>
       <c r="Q38" t="n">
-        <v>68</v>
+        <v>69</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2643,28 +3110,28 @@
         <v>6.88</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45548.55208333334</v>
+        <v>45551.38541666666</v>
       </c>
       <c r="H39" t="n">
-        <v>1787</v>
+        <v>1922.1</v>
       </c>
       <c r="I39" t="n">
         <v>1895.852012486689</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>1</v>
+        <v>3.833333333333333</v>
       </c>
       <c r="K39" t="n">
-        <v>1.05</v>
+        <v>-6.43</v>
       </c>
       <c r="L39" t="n">
-        <v>1.08</v>
+        <v>6.81</v>
       </c>
       <c r="M39" t="n">
-        <v>0.06</v>
+        <v>3.53</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>7.67</v>
       </c>
       <c r="O39" t="n">
         <v>-0.77</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S39" t="b">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>1</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>9.31</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45565.38541666666</v>
+        <v>45565.55208333334</v>
       </c>
       <c r="H40" t="n">
-        <v>1951</v>
+        <v>1910</v>
       </c>
       <c r="I40" t="n">
         <v>1943.377364877336</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>14</v>
+        <v>14.16666666666667</v>
       </c>
       <c r="K40" t="n">
-        <v>1.5</v>
+        <v>-0.63</v>
       </c>
       <c r="L40" t="n">
         <v>4.63</v>
@@ -2730,7 +3209,19 @@
         <v>1</v>
       </c>
       <c r="Q40" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -2757,28 +3248,28 @@
         <v>8.619999999999999</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45624.55208333334</v>
+        <v>45625.38541666666</v>
       </c>
       <c r="H41" t="n">
-        <v>1087.2</v>
+        <v>1282</v>
       </c>
       <c r="I41" t="n">
         <v>1148.811887476896</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>59</v>
+        <v>59.83333333333334</v>
       </c>
       <c r="K41" t="n">
-        <v>43.08</v>
+        <v>32.88</v>
       </c>
       <c r="L41" t="n">
         <v>2.25</v>
       </c>
       <c r="M41" t="n">
-        <v>3.2</v>
+        <v>5.68</v>
       </c>
       <c r="N41" t="n">
-        <v>10.01</v>
+        <v>21.41</v>
       </c>
       <c r="O41" t="n">
         <v>-3.44</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>80</v>
+        <v>81</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>3</v>
+      </c>
+      <c r="U41" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="42">
@@ -2814,25 +3317,25 @@
         <v>25.2</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45644.55208333334</v>
+        <v>45645.38541666666</v>
       </c>
       <c r="H42" t="n">
-        <v>1105</v>
+        <v>1071.35</v>
       </c>
       <c r="I42" t="n">
         <v>1096.744436989152</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>19.16666666666667</v>
+        <v>20</v>
       </c>
       <c r="K42" t="n">
-        <v>-13.81</v>
+        <v>-16.43</v>
       </c>
       <c r="L42" t="n">
-        <v>14.04</v>
+        <v>16.57</v>
       </c>
       <c r="M42" t="n">
-        <v>0.45</v>
+        <v>2.26</v>
       </c>
       <c r="N42" t="n">
         <v>3.77</v>
@@ -2844,7 +3347,19 @@
         <v>1</v>
       </c>
       <c r="Q42" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S42" t="b">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>1</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -2871,19 +3386,19 @@
         <v>12.21</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45670.55208333334</v>
+        <v>45671.38541666666</v>
       </c>
       <c r="H43" t="n">
-        <v>894</v>
+        <v>1005.6</v>
       </c>
       <c r="I43" t="n">
         <v>972.6064501808611</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>25.16666666666667</v>
+        <v>26</v>
       </c>
       <c r="K43" t="n">
-        <v>16.55</v>
+        <v>6.14</v>
       </c>
       <c r="L43" t="n">
         <v>4.45</v>
@@ -2892,7 +3407,7 @@
         <v>1.91</v>
       </c>
       <c r="N43" t="n">
-        <v>3.68</v>
+        <v>12.98</v>
       </c>
       <c r="O43" t="n">
         <v>-2.73</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2</v>
+      </c>
+      <c r="U43" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="44">
@@ -2928,19 +3455,19 @@
         <v>15.26</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45691.38541666666</v>
+        <v>45691.55208333334</v>
       </c>
       <c r="H44" t="n">
-        <v>976.8</v>
+        <v>969.5</v>
       </c>
       <c r="I44" t="n">
         <v>973.5867429827034</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>20</v>
+        <v>20.16666666666667</v>
       </c>
       <c r="K44" t="n">
-        <v>-2.86</v>
+        <v>-3.59</v>
       </c>
       <c r="L44" t="n">
         <v>10.75</v>
@@ -2958,7 +3485,19 @@
         <v>1</v>
       </c>
       <c r="Q44" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2985,25 +3524,25 @@
         <v>8.98</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45721.55208333334</v>
+        <v>45722.38541666666</v>
       </c>
       <c r="H45" t="n">
-        <v>849.95</v>
+        <v>850.4</v>
       </c>
       <c r="I45" t="n">
         <v>850.3836766487148</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>30</v>
+        <v>30.83333333333333</v>
       </c>
       <c r="K45" t="n">
-        <v>12.33</v>
+        <v>12.28</v>
       </c>
       <c r="L45" t="n">
         <v>6.11</v>
       </c>
       <c r="M45" t="n">
-        <v>1.44</v>
+        <v>2.22</v>
       </c>
       <c r="N45" t="n">
         <v>10.54</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -3042,28 +3593,28 @@
         <v>10.76</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45751.55208333334</v>
+        <v>45754.38541666666</v>
       </c>
       <c r="H46" t="n">
-        <v>925.95</v>
+        <v>861.85</v>
       </c>
       <c r="I46" t="n">
         <v>886.8804456511978</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>29.16666666666667</v>
+        <v>32</v>
       </c>
       <c r="K46" t="n">
-        <v>8.880000000000001</v>
+        <v>1.35</v>
       </c>
       <c r="L46" t="n">
         <v>5.18</v>
       </c>
       <c r="M46" t="n">
-        <v>0.7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="N46" t="n">
-        <v>3.57</v>
+        <v>5.18</v>
       </c>
       <c r="O46" t="n">
         <v>-0.79</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -3099,22 +3662,22 @@
         <v>11.64</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45762.55208333334</v>
+        <v>45763.38541666666</v>
       </c>
       <c r="H47" t="n">
-        <v>935.3</v>
+        <v>944.15</v>
       </c>
       <c r="I47" t="n">
         <v>937.8034796547042</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>9</v>
       </c>
       <c r="K47" t="n">
-        <v>-8.52</v>
+        <v>-9.550000000000001</v>
       </c>
       <c r="L47" t="n">
-        <v>9.300000000000001</v>
+        <v>10.92</v>
       </c>
       <c r="M47" t="n">
         <v>3.44</v>
@@ -3129,7 +3692,19 @@
         <v>1</v>
       </c>
       <c r="Q47" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S47" t="b">
+        <v>0</v>
+      </c>
+      <c r="T47" t="n">
+        <v>1</v>
+      </c>
+      <c r="U47" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -3156,22 +3731,22 @@
         <v>8.44</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45777.38541666666</v>
+        <v>45777.55208333334</v>
       </c>
       <c r="H48" t="n">
-        <v>912</v>
+        <v>895.65</v>
       </c>
       <c r="I48" t="n">
         <v>898.2413296631008</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>14</v>
+        <v>14.16666666666667</v>
       </c>
       <c r="K48" t="n">
-        <v>-3.41</v>
+        <v>-5.14</v>
       </c>
       <c r="L48" t="n">
-        <v>4.28</v>
+        <v>5.21</v>
       </c>
       <c r="M48" t="n">
         <v>0.01</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>2</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -3213,28 +3800,28 @@
         <v>8.73</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45779.55208333334</v>
+        <v>45782.38541666666</v>
       </c>
       <c r="H49" t="n">
-        <v>905.05</v>
+        <v>974.9</v>
       </c>
       <c r="I49" t="n">
         <v>973.8763253512348</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>2</v>
+        <v>4.833333333333333</v>
       </c>
       <c r="K49" t="n">
-        <v>-1.05</v>
+        <v>-8.85</v>
       </c>
       <c r="L49" t="n">
-        <v>4.05</v>
+        <v>12.04</v>
       </c>
       <c r="M49" t="n">
-        <v>0.71</v>
+        <v>0.85</v>
       </c>
       <c r="N49" t="n">
-        <v>1.05</v>
+        <v>7.18</v>
       </c>
       <c r="O49" t="n">
         <v>-2.75</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S49" t="b">
+        <v>0</v>
+      </c>
+      <c r="T49" t="n">
+        <v>1</v>
+      </c>
+      <c r="U49" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -3270,22 +3869,22 @@
         <v>11.33</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45785.38541666666</v>
+        <v>45785.55208333334</v>
       </c>
       <c r="H50" t="n">
-        <v>914.1</v>
+        <v>872</v>
       </c>
       <c r="I50" t="n">
         <v>881.4256829370548</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="K50" t="n">
-        <v>-6.24</v>
+        <v>-10.55</v>
       </c>
       <c r="L50" t="n">
-        <v>7.57</v>
+        <v>10.74</v>
       </c>
       <c r="M50" t="n">
         <v>2.25</v>
@@ -3300,7 +3899,19 @@
         <v>1</v>
       </c>
       <c r="Q50" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S50" t="b">
+        <v>0</v>
+      </c>
+      <c r="T50" t="n">
+        <v>1</v>
+      </c>
+      <c r="U50" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -3327,22 +3938,22 @@
         <v>12.08</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45789.55208333334</v>
+        <v>45790.38541666666</v>
       </c>
       <c r="H51" t="n">
-        <v>940</v>
+        <v>956.8</v>
       </c>
       <c r="I51" t="n">
         <v>947.5206228658238</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>4</v>
+        <v>4.833333333333333</v>
       </c>
       <c r="K51" t="n">
-        <v>-7.8</v>
+        <v>-9.720000000000001</v>
       </c>
       <c r="L51" t="n">
-        <v>8.369999999999999</v>
+        <v>11.66</v>
       </c>
       <c r="M51" t="n">
         <v>3.51</v>
@@ -3357,7 +3968,19 @@
         <v>1</v>
       </c>
       <c r="Q51" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S51" t="b">
+        <v>0</v>
+      </c>
+      <c r="T51" t="n">
+        <v>1</v>
+      </c>
+      <c r="U51" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -3384,25 +4007,25 @@
         <v>9.720000000000001</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45820.55208333334</v>
+        <v>45821.38541666666</v>
       </c>
       <c r="H52" t="n">
-        <v>1014</v>
+        <v>989</v>
       </c>
       <c r="I52" t="n">
         <v>1011.69203211897</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>30.16666666666667</v>
+        <v>31</v>
       </c>
       <c r="K52" t="n">
-        <v>5.98</v>
+        <v>3.37</v>
       </c>
       <c r="L52" t="n">
         <v>2.47</v>
       </c>
       <c r="M52" t="n">
-        <v>0.15</v>
+        <v>1.78</v>
       </c>
       <c r="N52" t="n">
         <v>3.41</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>2</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -3441,22 +4076,22 @@
         <v>6.65</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45834.55208333334</v>
+        <v>45835.38541666666</v>
       </c>
       <c r="H53" t="n">
-        <v>991.8</v>
+        <v>1017.1</v>
       </c>
       <c r="I53" t="n">
         <v>993.5665680994617</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K53" t="n">
-        <v>-0.28</v>
+        <v>-2.84</v>
       </c>
       <c r="L53" t="n">
-        <v>1.41</v>
+        <v>5.85</v>
       </c>
       <c r="M53" t="n">
         <v>1.56</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>2</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>5.94</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45862.55208333334</v>
+        <v>45863.38541666666</v>
       </c>
       <c r="H54" t="n">
-        <v>1020.9</v>
+        <v>990.9</v>
       </c>
       <c r="I54" t="n">
         <v>1000.529496413398</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>27.16666666666667</v>
+        <v>28</v>
       </c>
       <c r="K54" t="n">
-        <v>0.37</v>
+        <v>-2.58</v>
       </c>
       <c r="L54" t="n">
         <v>3.52</v>
@@ -3519,7 +4166,7 @@
         <v>0.58</v>
       </c>
       <c r="N54" t="n">
-        <v>2.15</v>
+        <v>4.08</v>
       </c>
       <c r="O54" t="n">
         <v>2.84</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S54" t="b">
+        <v>0</v>
+      </c>
+      <c r="T54" t="n">
+        <v>1</v>
+      </c>
+      <c r="U54" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -3555,19 +4214,19 @@
         <v>6.68</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45888.38541666666</v>
+        <v>45888.55208333334</v>
       </c>
       <c r="H55" t="n">
-        <v>959.35</v>
+        <v>971.8</v>
       </c>
       <c r="I55" t="n">
         <v>967.5277928463677</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>25</v>
+        <v>25.16666666666667</v>
       </c>
       <c r="K55" t="n">
-        <v>3.18</v>
+        <v>1.93</v>
       </c>
       <c r="L55" t="n">
         <v>3.39</v>
@@ -3585,7 +4244,19 @@
         <v>1</v>
       </c>
       <c r="Q55" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2</v>
+      </c>
+      <c r="U55" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="56">
@@ -3612,22 +4283,22 @@
         <v>6.36</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45895.55208333334</v>
+        <v>45897.38541666666</v>
       </c>
       <c r="H56" t="n">
-        <v>931</v>
+        <v>922.85</v>
       </c>
       <c r="I56" t="n">
         <v>929.1711183577403</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>7</v>
+        <v>8.833333333333334</v>
       </c>
       <c r="K56" t="n">
-        <v>-4.2</v>
+        <v>-5.04</v>
       </c>
       <c r="L56" t="n">
-        <v>4.71</v>
+        <v>5.63</v>
       </c>
       <c r="M56" t="n">
         <v>0.41</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S56" t="b">
+        <v>0</v>
+      </c>
+      <c r="T56" t="n">
+        <v>1</v>
+      </c>
+      <c r="U56" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -3669,28 +4352,28 @@
         <v>5.59</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45909.55208333334</v>
+        <v>45910.38541666666</v>
       </c>
       <c r="H57" t="n">
-        <v>946.5</v>
+        <v>965.05</v>
       </c>
       <c r="I57" t="n">
         <v>961.1044883853576</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>12.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K57" t="n">
-        <v>-2.56</v>
+        <v>-4.57</v>
       </c>
       <c r="L57" t="n">
-        <v>3.39</v>
+        <v>5.43</v>
       </c>
       <c r="M57" t="n">
         <v>0.78</v>
       </c>
       <c r="N57" t="n">
-        <v>1.66</v>
+        <v>2.01</v>
       </c>
       <c r="O57" t="n">
         <v>-0.71</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S57" t="b">
+        <v>0</v>
+      </c>
+      <c r="T57" t="n">
+        <v>1</v>
+      </c>
+      <c r="U57" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -3726,19 +4421,19 @@
         <v>4.99</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45926.55208333334</v>
+        <v>45929.38541666666</v>
       </c>
       <c r="H58" t="n">
-        <v>1051</v>
+        <v>1037.65</v>
       </c>
       <c r="I58" t="n">
         <v>1050.652070442982</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>16.16666666666667</v>
+        <v>19</v>
       </c>
       <c r="K58" t="n">
-        <v>8.91</v>
+        <v>7.52</v>
       </c>
       <c r="L58" t="n">
         <v>1.99</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S58" t="b">
+        <v>0</v>
+      </c>
+      <c r="T58" t="n">
+        <v>1</v>
+      </c>
+      <c r="U58" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -3783,28 +4490,28 @@
         <v>9.68</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>45958.55208333334</v>
+        <v>45959.38541666666</v>
       </c>
       <c r="H59" t="n">
-        <v>1005</v>
+        <v>1115.3</v>
       </c>
       <c r="I59" t="n">
         <v>1048.340755582745</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>29.16666666666667</v>
+        <v>30</v>
       </c>
       <c r="K59" t="n">
-        <v>3.15</v>
+        <v>-7.48</v>
       </c>
       <c r="L59" t="n">
-        <v>4.99</v>
+        <v>10.35</v>
       </c>
       <c r="M59" t="n">
-        <v>1.25</v>
+        <v>2.29</v>
       </c>
       <c r="N59" t="n">
-        <v>3.42</v>
+        <v>10.98</v>
       </c>
       <c r="O59" t="n">
         <v>-1.43</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>3</v>
+      </c>
+      <c r="U59" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="60">
@@ -3840,19 +4559,19 @@
         <v>10.62</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>45967.55208333334</v>
+        <v>45968.38541666666</v>
       </c>
       <c r="H60" t="n">
-        <v>1062</v>
+        <v>1047</v>
       </c>
       <c r="I60" t="n">
         <v>1056.084021712351</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>9</v>
       </c>
       <c r="K60" t="n">
-        <v>-4.78</v>
+        <v>-6.12</v>
       </c>
       <c r="L60" t="n">
         <v>9.25</v>
@@ -3870,7 +4589,19 @@
         <v>1</v>
       </c>
       <c r="Q60" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S60" t="b">
+        <v>0</v>
+      </c>
+      <c r="T60" t="n">
+        <v>1</v>
+      </c>
+      <c r="U60" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -3897,19 +4628,19 @@
         <v>8.49</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46003.55208333334</v>
+        <v>46006.38541666666</v>
       </c>
       <c r="H61" t="n">
-        <v>1038.1</v>
+        <v>1050.2</v>
       </c>
       <c r="I61" t="n">
         <v>1041.624184820566</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>35.16666666666666</v>
+        <v>38</v>
       </c>
       <c r="K61" t="n">
-        <v>0.85</v>
+        <v>-0.31</v>
       </c>
       <c r="L61" t="n">
         <v>5.53</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>2</v>
+      </c>
+      <c r="U61" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -3954,28 +4697,28 @@
         <v>5.52</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46029.55208333334</v>
+        <v>46030.38541666666</v>
       </c>
       <c r="H62" t="n">
-        <v>1018.9</v>
+        <v>995.7</v>
       </c>
       <c r="I62" t="n">
         <v>1001.581830019074</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>23.16666666666667</v>
+        <v>24</v>
       </c>
       <c r="K62" t="n">
-        <v>-2.98</v>
+        <v>-5.19</v>
       </c>
       <c r="L62" t="n">
-        <v>4.94</v>
+        <v>5.73</v>
       </c>
       <c r="M62" t="n">
         <v>0.23</v>
       </c>
       <c r="N62" t="n">
-        <v>1.91</v>
+        <v>3.44</v>
       </c>
       <c r="O62" t="n">
         <v>0.5600000000000001</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>2</v>
+      </c>
+      <c r="U62" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="63">
@@ -4011,28 +4766,28 @@
         <v>5.34</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>46055.55208333334</v>
+        <v>46056.38541666666</v>
       </c>
       <c r="H63" t="n">
-        <v>844</v>
+        <v>930.5</v>
       </c>
       <c r="I63" t="n">
         <v>879.767698068712</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>25.16666666666667</v>
+        <v>26</v>
       </c>
       <c r="K63" t="n">
-        <v>15.24</v>
+        <v>6.55</v>
       </c>
       <c r="L63" t="n">
         <v>2.85</v>
       </c>
       <c r="M63" t="n">
-        <v>1.38</v>
+        <v>9.48</v>
       </c>
       <c r="N63" t="n">
-        <v>4.52</v>
+        <v>10.43</v>
       </c>
       <c r="O63" t="n">
         <v>-3.44</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>2</v>
+      </c>
+      <c r="U63" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -4068,25 +4835,25 @@
         <v>12.39</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>46080.55208333334</v>
+        <v>46083.38541666666</v>
       </c>
       <c r="H64" t="n">
-        <v>943</v>
+        <v>885.9</v>
       </c>
       <c r="I64" t="n">
         <v>940.6053680973635</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>24.16666666666667</v>
+        <v>27</v>
       </c>
       <c r="K64" t="n">
-        <v>1.34</v>
+        <v>-4.79</v>
       </c>
       <c r="L64" t="n">
-        <v>3.28</v>
+        <v>4.87</v>
       </c>
       <c r="M64" t="n">
-        <v>0.92</v>
+        <v>2.97</v>
       </c>
       <c r="N64" t="n">
         <v>4.74</v>
@@ -4098,7 +4865,19 @@
         <v>1</v>
       </c>
       <c r="Q64" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>2</v>
+      </c>
+      <c r="U64" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -4125,19 +4904,19 @@
         <v>9.890000000000001</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>46114.55208333334</v>
+        <v>46118.38541666666</v>
       </c>
       <c r="H65" t="n">
-        <v>854</v>
+        <v>912.55</v>
       </c>
       <c r="I65" t="n">
         <v>874.8056954346326</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>31.16666666666667</v>
+        <v>35</v>
       </c>
       <c r="K65" t="n">
-        <v>3.6</v>
+        <v>-3.01</v>
       </c>
       <c r="L65" t="n">
         <v>4.63</v>
@@ -4146,7 +4925,7 @@
         <v>2.87</v>
       </c>
       <c r="N65" t="n">
-        <v>5.88</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="O65" t="n">
         <v>-3.94</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>2</v>
+      </c>
+      <c r="U65" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -4182,19 +4973,19 @@
         <v>12.68</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>46225.38541666666</v>
+        <v>46225.55208333334</v>
       </c>
       <c r="H66" t="n">
-        <v>1516</v>
+        <v>1472</v>
       </c>
       <c r="I66" t="n">
         <v>1488.617745787657</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>107</v>
+        <v>107.1666666666667</v>
       </c>
       <c r="K66" t="n">
-        <v>66.13</v>
+        <v>61.31</v>
       </c>
       <c r="L66" t="n">
         <v>6.19</v>
@@ -4212,7 +5003,19 @@
         <v>1</v>
       </c>
       <c r="Q66" t="n">
-        <v>147</v>
+        <v>148</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S66" t="b">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>4</v>
+      </c>
+      <c r="U66" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="67">
@@ -4239,19 +5042,19 @@
         <v>8.93</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>46273.55208333334</v>
+        <v>46274.38541666666</v>
       </c>
       <c r="H67" t="n">
-        <v>1297</v>
+        <v>1331.1</v>
       </c>
       <c r="I67" t="n">
         <v>1323.525003073001</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>48</v>
+        <v>48.83333333333334</v>
       </c>
       <c r="K67" t="n">
-        <v>11.89</v>
+        <v>9.57</v>
       </c>
       <c r="L67" t="n">
         <v>3.6</v>
@@ -4269,7 +5072,19 @@
         <v>1</v>
       </c>
       <c r="Q67" t="n">
-        <v>69</v>
+        <v>70</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>3</v>
+      </c>
+      <c r="U67" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="68">
@@ -4296,28 +5111,28 @@
         <v>6.72</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>46290.55208333334</v>
+        <v>46293.38541666666</v>
       </c>
       <c r="H68" t="n">
-        <v>1293.5</v>
+        <v>1237.8</v>
       </c>
       <c r="I68" t="n">
         <v>1250.486408335413</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>16.16666666666667</v>
+        <v>19</v>
       </c>
       <c r="K68" t="n">
-        <v>-2.82</v>
+        <v>-7.01</v>
       </c>
       <c r="L68" t="n">
-        <v>6.42</v>
+        <v>7.14</v>
       </c>
       <c r="M68" t="n">
         <v>0.5</v>
       </c>
       <c r="N68" t="n">
-        <v>2.1</v>
+        <v>4.6</v>
       </c>
       <c r="O68" t="n">
         <v>1.26</v>
@@ -4326,7 +5141,19 @@
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S68" t="b">
+        <v>0</v>
+      </c>
+      <c r="T68" t="n">
+        <v>1</v>
+      </c>
+      <c r="U68" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -4353,28 +5180,28 @@
         <v>8.42</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>46300.55208333334</v>
+        <v>46301.38541666666</v>
       </c>
       <c r="H69" t="n">
-        <v>1282</v>
+        <v>1320.2</v>
       </c>
       <c r="I69" t="n">
         <v>1308.953878000167</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K69" t="n">
-        <v>-3.57</v>
+        <v>-6.66</v>
       </c>
       <c r="L69" t="n">
-        <v>5.31</v>
+        <v>7.4</v>
       </c>
       <c r="M69" t="n">
         <v>0.34</v>
       </c>
       <c r="N69" t="n">
-        <v>1.7</v>
+        <v>2.44</v>
       </c>
       <c r="O69" t="n">
         <v>-4.6</v>
@@ -4383,7 +5210,19 @@
         <v>1</v>
       </c>
       <c r="Q69" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S69" t="b">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
+        <v>2</v>
+      </c>
+      <c r="U69" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="70">
@@ -4410,28 +5249,28 @@
         <v>7.49</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>46302.55208333334</v>
+        <v>46303.38541666666</v>
       </c>
       <c r="H70" t="n">
-        <v>1342.7</v>
+        <v>1223.1</v>
       </c>
       <c r="I70" t="n">
         <v>1253.554028480638</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>1.166666666666667</v>
+        <v>2</v>
       </c>
       <c r="K70" t="n">
-        <v>1.7</v>
+        <v>-7.35</v>
       </c>
       <c r="L70" t="n">
-        <v>3.01</v>
+        <v>8.5</v>
       </c>
       <c r="M70" t="n">
         <v>0.02</v>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>7.61</v>
       </c>
       <c r="O70" t="n">
         <v>2.44</v>
@@ -4440,7 +5279,19 @@
         <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S70" t="b">
+        <v>0</v>
+      </c>
+      <c r="T70" t="n">
+        <v>1</v>
+      </c>
+      <c r="U70" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -4491,6 +5342,12 @@
       <c r="Q71" t="n">
         <v>26</v>
       </c>
+      <c r="R71" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S71" t="inlineStr"/>
+      <c r="T71" t="inlineStr"/>
+      <c r="U71" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6593,7 +7450,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>24.1</v>
+        <v>25.1</v>
       </c>
     </row>
     <row r="6">
@@ -6603,7 +7460,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>20</v>
+        <v>20.2</v>
       </c>
     </row>
     <row r="7">
@@ -6613,7 +7470,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>107</v>
+        <v>107.2</v>
       </c>
     </row>
     <row r="8">
@@ -6623,7 +7480,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="9">
@@ -6633,7 +7490,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>30.2</v>
+        <v>32</v>
       </c>
     </row>
     <row r="10">
@@ -6643,7 +7500,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>48.3</v>
+        <v>49</v>
       </c>
     </row>
     <row r="11">
@@ -6653,7 +7510,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="12">
@@ -6663,7 +7520,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="13">
@@ -6673,7 +7530,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>72.5</v>
+        <v>69.59999999999999</v>
       </c>
     </row>
     <row r="14">
@@ -6683,7 +7540,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>6.36</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -6693,7 +7550,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7.69</v>
+        <v>3.77</v>
       </c>
     </row>
     <row r="16">
@@ -6703,7 +7560,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>5</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="17">
@@ -6713,7 +7570,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>76.61</v>
+        <v>73.59999999999999</v>
       </c>
     </row>
     <row r="18">
@@ -6723,7 +7580,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>50.7</v>
+        <v>31.9</v>
       </c>
     </row>
     <row r="19">
@@ -6733,7 +7590,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5.91</v>
+        <v>7.45</v>
       </c>
     </row>
     <row r="20">
@@ -6743,7 +7600,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4.97</v>
+        <v>6.15</v>
       </c>
     </row>
     <row r="21">
@@ -6763,7 +7620,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>33</v>
+        <v>47</v>
       </c>
     </row>
     <row r="23">
@@ -6773,7 +7630,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
     </row>
     <row r="24">
@@ -6783,7 +7640,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.81</v>
+        <v>2.24</v>
       </c>
     </row>
     <row r="25">
@@ -6793,7 +7650,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>7.56</v>
+        <v>9.48</v>
       </c>
     </row>
     <row r="26">
@@ -6803,7 +7660,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4.56</v>
+        <v>6.28</v>
       </c>
     </row>
     <row r="27">
@@ -6813,7 +7670,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>11.3</v>
+        <v>21.41</v>
       </c>
     </row>
     <row r="28">
@@ -6823,7 +7680,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>35</v>
+        <v>50</v>
       </c>
     </row>
     <row r="29">
